--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/guild_clerk.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/guild_clerk.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr autoCompressPictures="1"/>
-  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="1" r:id="rId3"/>
+    <sheet name="1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
-    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -203,45 +203,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unfortunately, we cannot approve your promotion at this time.</t>
-  </si>
-  <si>
-    <t xml:space="preserve"/>
-  </si>
-  <si>
-    <t xml:space="preserve">{哎呀}，你好像不是#guild的成员{。}。你是怎么进来的{。}？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你想加入#guild成为其中一员的话，最好先和玛丽安女士搭话{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#guild欢迎回来，#pc。你现在的等级是#guild_title{。}。今天有什么事{。}？</t>
-  </si>
-  <si>
-    <t xml:space="preserve">告诉我公会的事</t>
-  </si>
-  <si>
-    <t xml:space="preserve">想获得晋升</t>
-  </si>
-  <si>
-    <t xml:space="preserve">盗贼公会「夜之白布」是在黑暗世界生活的不正经人群的圣域{。}。这里不会追究任何罪人的过去。我们的公会会长还有「使夜降临之人」这样的别名，据说从来没人看到过他的本来面目{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">魔法师公会具备其他公会所没有的优秀教育系统{。}。从提里斯各地来的学生们为寻求知识聚集在一起{。}。校长约格虽然是公认的“俗人”，但在金钱和政治方面确实是个天才{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">战士公会里聚集着很多以自己实力为傲的冒险者{。}。会长托兰虽然很严厉，但为了保护公会的成员，他甚至敢和整个国家开战{。}。托他的福，我们都像家人一样紧密团结在一起{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">商人公会会为商人们提供支持，是保证商人们安全、公正交易的组织{。}。玛丽安女士虽然有点可怕{。}，但她也是仅凭一代就在提里斯发财的厉害女商人{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">对#guild的贡献度足够的状态下和我对话，就能增加公会中的排名{。}。排名提升后，就可以使用高级服务，还会有各种奖励，请加油提升排名吧{。}。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">你已经满足了下一次晋升等级的条件{。}。恭喜你晋升了{。}！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">很遗憾{。}，现在还不能认可你的晋升{。}。</t>
   </si>
 </sst>
 </file>
@@ -263,19 +224,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family/>
+      <family val="0"/>
       <charset val="128"/>
     </font>
     <font>
@@ -301,7 +262,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -310,50 +271,50 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment/>
-      <protection locked="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -367,13 +328,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <name val="游ゴシック"/>
+        <charset val="128"/>
+        <family val="2"/>
         <color rgb="FFCC0000"/>
-        <name val="游ゴシック"/>
-        <family val="2"/>
-        <charset val="128"/>
       </font>
       <fill>
-        <patternFill patternType="solid">
+        <patternFill>
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -549,25 +510,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <sheetPr>
-    <pageSetUpPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L42"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="2" width="8.85" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.56" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32.13" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.85" style="1" customWidth="1"/>
-    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
-    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
-    <col min="10" max="10" width="42.14" style="1" customWidth="1"/>
-    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="42.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
   </cols>
   <sheetData>
-    <row r="1" ht="12.8">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -605,28 +566,28 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="12.8">
-      <c r="I2" s="1">
-        <f>MAX(I4:I1048576)</f>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I2" s="1" t="n">
+        <f aca="false">MAX(I4:I1048576)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="5" ht="12.8">
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" ht="12.8">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" ht="12.8">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" ht="12.8">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C10" s="1" t="s">
         <v>15</v>
       </c>
@@ -636,7 +597,7 @@
       <c r="E10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="1" t="n">
         <v>9</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -645,11 +606,8 @@
       <c r="K10" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L10" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="11" ht="12.8">
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C11" s="1" t="s">
         <v>20</v>
       </c>
@@ -659,7 +617,7 @@
       <c r="E11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" s="1" t="n">
         <v>10</v>
       </c>
       <c r="J11" s="1" t="s">
@@ -668,11 +626,8 @@
       <c r="K11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L11" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="12" ht="12.8">
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C12" s="1" t="s">
         <v>22</v>
       </c>
@@ -682,7 +637,7 @@
       <c r="E12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12" s="1" t="n">
         <v>11</v>
       </c>
       <c r="J12" s="1" t="s">
@@ -691,11 +646,8 @@
       <c r="K12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L12" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="13" ht="12.8">
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C13" s="1" t="s">
         <v>24</v>
       </c>
@@ -705,7 +657,7 @@
       <c r="E13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13" s="1" t="n">
         <v>12</v>
       </c>
       <c r="J13" s="1" t="s">
@@ -714,15 +666,12 @@
       <c r="K13" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="L13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="14" ht="12.8">
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D14" s="3"/>
     </row>
-    <row r="15" ht="12.8">
-      <c r="I15" s="1">
+    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I15" s="1" t="n">
         <v>1</v>
       </c>
       <c r="J15" s="1" t="s">
@@ -731,18 +680,15 @@
       <c r="K15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L15" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="17" ht="12.8">
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17" s="1" t="n">
         <v>2</v>
       </c>
       <c r="J17" s="1" t="s">
@@ -751,11 +697,8 @@
       <c r="K17" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" ht="12.8">
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="1" t="s">
         <v>34</v>
       </c>
@@ -765,7 +708,7 @@
       <c r="E18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I18" s="1">
+      <c r="I18" s="1" t="n">
         <v>13</v>
       </c>
       <c r="J18" s="1" t="s">
@@ -774,11 +717,8 @@
       <c r="K18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L18" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="19" ht="12.8">
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E19" s="1" t="s">
         <v>38</v>
       </c>
@@ -786,26 +726,26 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" ht="12.8">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E20" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" ht="12.8">
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E21" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="24" ht="12.8">
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" ht="12.8">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="1">
+      <c r="I25" s="1" t="n">
         <v>4</v>
       </c>
       <c r="J25" s="1" t="s">
@@ -814,15 +754,12 @@
       <c r="K25" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L25" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" ht="12.8">
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I26" s="1">
+      <c r="I26" s="1" t="n">
         <v>5</v>
       </c>
       <c r="J26" s="1" t="s">
@@ -831,15 +768,12 @@
       <c r="K26" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="L26" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" ht="12.8">
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="1">
+      <c r="I27" s="1" t="n">
         <v>6</v>
       </c>
       <c r="J27" s="1" t="s">
@@ -848,15 +782,12 @@
       <c r="K27" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="L27" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="28" ht="12.8">
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="1">
+      <c r="I28" s="1" t="n">
         <v>8</v>
       </c>
       <c r="J28" s="1" t="s">
@@ -865,12 +796,9 @@
       <c r="K28" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="L28" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" ht="12.8">
-      <c r="I29" s="1">
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I29" s="1" t="n">
         <v>7</v>
       </c>
       <c r="J29" s="1" t="s">
@@ -879,21 +807,18 @@
       <c r="K29" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="L29" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="30" ht="12.8">
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="33" ht="12.8">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="34" ht="12.8">
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="1" t="s">
         <v>53</v>
       </c>
@@ -901,7 +826,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" ht="12.8">
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="E35" s="1" t="s">
         <v>55</v>
       </c>
@@ -909,8 +834,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" ht="12.8">
-      <c r="I36" s="1">
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I36" s="1" t="n">
         <v>14</v>
       </c>
       <c r="J36" s="1" t="s">
@@ -919,22 +844,19 @@
       <c r="K36" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="L36" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="38" ht="12.8">
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="40" ht="12.8">
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="41" ht="12.8">
-      <c r="I41" s="1">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I41" s="1" t="n">
         <v>15</v>
       </c>
       <c r="J41" s="1" t="s">
@@ -943,23 +865,20 @@
       <c r="K41" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="L41" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="42" ht="12.8">
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="1" t="s">
         <v>58</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
   </conditionalFormatting>
-  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>

--- a/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/guild_clerk.xlsx
+++ b/new original/_Lang_Chinese/Lang/CN/Dialog/Drama/guild_clerk.xlsx
@@ -2,25 +2,25 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+  <workbookPr autoCompressPictures="1"/>
+  <workbookProtection lockStructure="0" lockWindows="0" lockRevision="0"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView windowWidth="16384" windowHeight="8192" tabRatio="500"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="1" sheetId="1" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
+  <calcPr calcMode="auto" fullCalcOnLoad="0" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.001" fullPrecision="1" calcCompleted="0" calcOnSave="0" concurrentCalc="0" forceFullCalc="0"/>
   <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1"/>
+    <ext uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr xmlns:loext="http://schemas.libreoffice.org/" stringRefSyntax="CalcA1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="74">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -203,6 +203,45 @@
   </si>
   <si>
     <t xml:space="preserve">Unfortunately, we cannot approve your promotion at this time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"/>
+  </si>
+  <si>
+    <t xml:space="preserve">{哎呀}，你好像不是#guild的成员{。}。你是怎么进来的{。}？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你想加入#guild成为其中一员的话，最好先和玛丽安女士搭话{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#guild欢迎回来，#pc。你现在的等级是#guild_title{。}。今天有什么事{。}？</t>
+  </si>
+  <si>
+    <t xml:space="preserve">告诉我公会的事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">想获得晋升</t>
+  </si>
+  <si>
+    <t xml:space="preserve">盗贼公会「夜之白布」是在黑暗世界生活的不正经人群的圣域{。}。这里不会追究任何罪人的过去。我们的公会会长还有「使夜降临之人」这样的别名，据说从来没人看到过他的本来面目{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">魔法师公会具备其他公会所没有的优秀教育系统{。}。从提里斯各地来的学生们为寻求知识聚集在一起{。}。校长约格虽然是公认的“俗人”，但在金钱和政治方面确实是个天才{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">战士公会里聚集着很多以自己实力为傲的冒险者{。}。会长托兰虽然很严厉，但为了保护公会的成员，他甚至敢和整个国家开战{。}。托他的福，我们都像家人一样紧密团结在一起{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">商人公会会为商人们提供支持，是保证商人们安全、公正交易的组织{。}。玛丽安女士虽然有点可怕{。}，但她也是仅凭一代就在提里斯发财的厉害女商人{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">对#guild的贡献度足够的状态下和我对话，就能增加公会中的排名{。}。排名提升后，就可以使用高级服务，还会有各种奖励，请加油提升排名吧{。}。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">你已经满足了下一次晋升等级的条件{。}。恭喜你晋升了{。}！</t>
+  </si>
+  <si>
+    <t xml:space="preserve">很遗憾{。}，现在还不能认可你的晋升{。}。</t>
   </si>
 </sst>
 </file>
@@ -224,19 +263,19 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
+      <family/>
       <charset val="128"/>
     </font>
     <font>
@@ -262,7 +301,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -271,50 +310,50 @@
     </border>
   </borders>
   <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="0">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment/>
+      <protection locked="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -328,13 +367,13 @@
   <dxfs count="1">
     <dxf>
       <font>
+        <color rgb="FFCC0000"/>
         <name val="游ゴシック"/>
+        <family val="2"/>
         <charset val="128"/>
-        <family val="2"/>
-        <color rgb="FFCC0000"/>
       </font>
       <fill>
-        <patternFill>
+        <patternFill patternType="solid">
           <bgColor rgb="FFFFCCCC"/>
         </patternFill>
       </fill>
@@ -510,25 +549,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L42"/>
-  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="32.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="7.09"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="42.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="53.28"/>
+    <col min="1" max="2" width="8.85" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.56" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32.13" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11.85" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85" style="1" customWidth="1"/>
+    <col min="8" max="9" width="7.09" style="1" customWidth="1"/>
+    <col min="10" max="10" width="42.14" style="1" customWidth="1"/>
+    <col min="11" max="11" width="53.28" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" ht="12.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -566,28 +605,28 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I2" s="1" t="n">
-        <f aca="false">MAX(I4:I1048576)</f>
+    <row r="2" ht="12.8">
+      <c r="I2" s="1">
+        <f>MAX(I4:I1048576)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" ht="12.8">
       <c r="E5" s="1" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" ht="12.8">
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" ht="12.8">
       <c r="A8" s="1" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" ht="12.8">
       <c r="C10" s="1" t="s">
         <v>15</v>
       </c>
@@ -597,7 +636,7 @@
       <c r="E10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I10" s="1" t="n">
+      <c r="I10" s="1">
         <v>9</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -606,8 +645,11 @@
       <c r="K10" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L10" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" ht="12.8">
       <c r="C11" s="1" t="s">
         <v>20</v>
       </c>
@@ -617,7 +659,7 @@
       <c r="E11" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="1" t="n">
+      <c r="I11" s="1">
         <v>10</v>
       </c>
       <c r="J11" s="1" t="s">
@@ -626,8 +668,11 @@
       <c r="K11" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12" ht="12.8">
       <c r="C12" s="1" t="s">
         <v>22</v>
       </c>
@@ -637,7 +682,7 @@
       <c r="E12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="1" t="n">
+      <c r="I12" s="1">
         <v>11</v>
       </c>
       <c r="J12" s="1" t="s">
@@ -646,8 +691,11 @@
       <c r="K12" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" ht="12.8">
       <c r="C13" s="1" t="s">
         <v>24</v>
       </c>
@@ -657,7 +705,7 @@
       <c r="E13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I13" s="1" t="n">
+      <c r="I13" s="1">
         <v>12</v>
       </c>
       <c r="J13" s="1" t="s">
@@ -666,12 +714,15 @@
       <c r="K13" s="1" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" ht="12.8">
       <c r="D14" s="3"/>
     </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I15" s="1" t="n">
+    <row r="15" ht="12.8">
+      <c r="I15" s="1">
         <v>1</v>
       </c>
       <c r="J15" s="1" t="s">
@@ -680,15 +731,18 @@
       <c r="K15" s="1" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" ht="12.8">
       <c r="B17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I17" s="1" t="n">
+      <c r="I17" s="1">
         <v>2</v>
       </c>
       <c r="J17" s="1" t="s">
@@ -697,8 +751,11 @@
       <c r="K17" s="1" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" ht="12.8">
       <c r="B18" s="1" t="s">
         <v>34</v>
       </c>
@@ -708,7 +765,7 @@
       <c r="E18" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="I18" s="1" t="n">
+      <c r="I18" s="1">
         <v>13</v>
       </c>
       <c r="J18" s="1" t="s">
@@ -717,8 +774,11 @@
       <c r="K18" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L18" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" ht="12.8">
       <c r="E19" s="1" t="s">
         <v>38</v>
       </c>
@@ -726,26 +786,26 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" ht="12.8">
       <c r="E20" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" ht="12.8">
       <c r="E21" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" ht="12.8">
       <c r="A24" s="1" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" ht="12.8">
       <c r="C25" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I25" s="1" t="n">
+      <c r="I25" s="1">
         <v>4</v>
       </c>
       <c r="J25" s="1" t="s">
@@ -754,12 +814,15 @@
       <c r="K25" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" ht="12.8">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I26" s="1" t="n">
+      <c r="I26" s="1">
         <v>5</v>
       </c>
       <c r="J26" s="1" t="s">
@@ -768,12 +831,15 @@
       <c r="K26" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L26" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" ht="12.8">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I27" s="1" t="n">
+      <c r="I27" s="1">
         <v>6</v>
       </c>
       <c r="J27" s="1" t="s">
@@ -782,12 +848,15 @@
       <c r="K27" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" ht="12.8">
       <c r="C28" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="I28" s="1" t="n">
+      <c r="I28" s="1">
         <v>8</v>
       </c>
       <c r="J28" s="1" t="s">
@@ -796,9 +865,12 @@
       <c r="K28" s="1" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I29" s="1" t="n">
+      <c r="L28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" ht="12.8">
+      <c r="I29" s="1">
         <v>7</v>
       </c>
       <c r="J29" s="1" t="s">
@@ -807,18 +879,21 @@
       <c r="K29" s="1" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L29" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" ht="12.8">
       <c r="B30" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" ht="12.8">
       <c r="A33" s="1" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" ht="12.8">
       <c r="B34" s="1" t="s">
         <v>53</v>
       </c>
@@ -826,7 +901,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" ht="12.8">
       <c r="E35" s="1" t="s">
         <v>55</v>
       </c>
@@ -834,8 +909,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I36" s="1" t="n">
+    <row r="36" ht="12.8">
+      <c r="I36" s="1">
         <v>14</v>
       </c>
       <c r="J36" s="1" t="s">
@@ -844,19 +919,22 @@
       <c r="K36" s="4" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L36" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" ht="12.8">
       <c r="B38" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" ht="12.8">
       <c r="A40" s="1" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I41" s="1" t="n">
+    <row r="41" ht="12.8">
+      <c r="I41" s="1">
         <v>15</v>
       </c>
       <c r="J41" s="1" t="s">
@@ -865,20 +943,23 @@
       <c r="K41" s="4" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L41" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" ht="12.8">
       <c r="B42" s="1" t="s">
         <v>58</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="I4:I1048576">
-    <cfRule type="duplicateValues" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter>
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
